--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5287-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5287-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C42495F-0931-4140-A892-21CC8A9A5748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB069A99-8073-43A8-8649-25F1078B5739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{6C3AACE6-3CA4-4D73-977E-7DEBE5396D21}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{B0E05847-D3A1-4F85-9A32-66F7712D537A}"/>
   </bookViews>
   <sheets>
     <sheet name="5287-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1538,21 +1538,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82925FD-6177-4168-ABAE-8A345C65CA94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC1B1BF-7306-4370-B627-E4BD0D9AF189}">
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" customWidth="1"/>
-    <col min="4" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="9.25" customWidth="1"/>
+    <col min="4" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +1580,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1610,7 +1610,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1706,7 +1706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2025</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="43">
         <v>2024</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="45" t="s">
         <v>25</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="46"/>
       <c r="B11" s="22" t="s">
         <v>31</v>
@@ -2060,7 +2060,7 @@
       <c r="Q11" s="50"/>
       <c r="R11" s="50"/>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="41">
         <v>2023</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="55" t="s">
         <v>25</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="56"/>
       <c r="B15" s="24" t="s">
         <v>31</v>
@@ -2248,7 +2248,7 @@
       <c r="Q15" s="60"/>
       <c r="R15" s="60"/>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="43">
         <v>2022</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>25</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>2021</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="43">
         <v>2020</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="41">
         <v>2019</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="43">
         <v>2018</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="41">
         <v>2017</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="43">
         <v>2016</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <v>2015</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="43">
         <v>2014</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="41">
         <v>2013</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="43">
         <v>2012</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="41">
         <v>2011</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>40</v>
       </c>
